--- a/bases de datos planes y programas/planes_matematica.xlsx
+++ b/bases de datos planes y programas/planes_matematica.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Planes Curriculares" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planes Curriculares'!$A$1:$G$241</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -469,12 +471,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9624,25 +9626,145 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
+          <t>Resolver problemas</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>OA a</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>• Utilizan modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.
+• Identifican los intervalos donde el modelo exponencial o logarítmico tiene sentido, según la situación de crecimiento o decrecimiento.
+• Varían parámetros para ajustar un modelo exponencial o logarítmico según la situación.
+• Construyen modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>III Medio</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Resolver problemas</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>OA a</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>• Utilizan relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia para determinar medidas de objetos geométricos.
+• Justifican el uso de propiedades sobre ángulos, arcos o cuerdas para resolver un problema.
+• Explican las relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia, utilizando dibujos, esquemas o proposiciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>III Medio</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>Resolver problemas</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>OA a</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>• Representan números complejos en el plano, relacionando con vectores e identificando las partes reales e imaginarias.
+• Utilizan los números complejos y sus representaciones pictóricas y simbólicas para encontrar solución a ecuaciones.
+• Determinan la distancia de números complejos de forma simbólica y pictórica.
+• Representan la operatoria de números complejos de forma simbólica y en el plano cartesiano.
+• Utilizan los números complejos y su operatoria para resolver problemas en modelos relacionados con los circuitos eléctricos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>III Medio</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
           <t>Argumentar y Comunicar</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>OA c</t>
         </is>
       </c>
-      <c r="E225" s="5" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Tomar decisiones fundamentadas en evidencia estadística y/o en la evaluación de resultados obtenidos a partir de un modelo probabilístico.</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G225" s="5" t="inlineStr">
+      <c r="G228" s="3" t="inlineStr">
         <is>
           <t>• Extraen e interpretan información estadística, calculando medidas de dispersión para comparar situaciones.
 • Analizan datos, calculando las medidas de dispersión para tomar decisiones.
@@ -9652,38 +9774,38 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
         <is>
           <t>III Medio</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
         <is>
           <t>Argumentar y Comunicar</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D229" s="4" t="inlineStr">
         <is>
           <t>OA d</t>
         </is>
       </c>
-      <c r="E226" s="3" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>Argumentar, utilizando lenguaje simbólico y diferentes representaciones, para justificar la veracidad o falsedad de una conjetura, y evaluar el alcance y los límites de los argumentos utilizados.</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F229" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G226" s="3" t="inlineStr">
+      <c r="G229" s="5" t="inlineStr">
         <is>
           <t>• Extraen e interpretan información estadística, calculando medidas de dispersión para comparar situaciones.
 • Analizan datos, calculando las medidas de dispersión para tomar decisiones.
@@ -9693,38 +9815,77 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>III Medio</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C227" s="5" t="inlineStr">
-        <is>
-          <t>Resolver problemas</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
-        <is>
-          <t>OA a</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="inlineStr">
-        <is>
-          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
-        </is>
-      </c>
-      <c r="F227" s="4" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Argumentar y Comunicar</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>OA d</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Argumentar, utilizando lenguaje simbólico y diferentes representaciones para justificar la veracidad o falsedad de una conjetura, y evaluar el alcance y los límites de los argumentos utilizados.</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>• Utilizan relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia para determinar medidas de objetos geométricos.
+• Justifican el uso de propiedades sobre ángulos, arcos o cuerdas para resolver un problema.
+• Explican las relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia, utilizando dibujos, esquemas o proposiciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>III Medio</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Modelar</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>OA e</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Construir modelos, realizando conexiones entre variables para predecir posibles escenarios de solución a un problema, y tomar decisiones fundamentadas.</t>
+        </is>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G227" s="5" t="inlineStr">
+      <c r="G231" s="5" t="inlineStr">
         <is>
           <t>• Utilizan modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.
 • Identifican los intervalos donde el modelo exponencial o logarítmico tiene sentido, según la situación de crecimiento o decrecimiento.
@@ -9733,202 +9894,43 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>III Medio</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
         <is>
           <t>Modelar</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>OA e</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>Construir modelos, realizando conexiones entre variables para predecir posibles escenarios de solución a un problema, y tomar decisiones fundamentadas.</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>OA f</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>Evaluar modelos para estudiar un fenómeno, analizando críticamente las simplificaciones requeridas y considerando las limitaciones de aquellos.</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
         <is>
           <t>• Utilizan modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.
 • Identifican los intervalos donde el modelo exponencial o logarítmico tiene sentido, según la situación de crecimiento o decrecimiento.
 • Varían parámetros para ajustar un modelo exponencial o logarítmico según la situación.
 • Construyen modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>III Medio</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>Modelar</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr">
-        <is>
-          <t>OA f</t>
-        </is>
-      </c>
-      <c r="E229" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar modelos para estudiar un fenómeno, analizando críticamente las simplificaciones requeridas y considerando las limitaciones de aquellos.</t>
-        </is>
-      </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>• Utilizan modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.
-• Identifican los intervalos donde el modelo exponencial o logarítmico tiene sentido, según la situación de crecimiento o decrecimiento.
-• Varían parámetros para ajustar un modelo exponencial o logarítmico según la situación.
-• Construyen modelos de situaciones de crecimiento y decrecimiento que involucran las funciones exponencial y logarítmica, para determinar valores o hacer proyecciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>III Medio</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>Resolver problemas</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>OA a</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>• Utilizan relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia para determinar medidas de objetos geométricos.
-• Justifican el uso de propiedades sobre ángulos, arcos o cuerdas para resolver un problema.
-• Explican las relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia, utilizando dibujos, esquemas o proposiciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>III Medio</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>Argumentar y Comunicar</t>
-        </is>
-      </c>
-      <c r="D231" s="4" t="inlineStr">
-        <is>
-          <t>OA d</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>Argumentar, utilizando lenguaje simbólico y diferentes representaciones para justificar la veracidad o falsedad de una conjetura, y evaluar el alcance y los límites de los argumentos utilizados.</t>
-        </is>
-      </c>
-      <c r="F231" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>• Utilizan relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia para determinar medidas de objetos geométricos.
-• Justifican el uso de propiedades sobre ángulos, arcos o cuerdas para resolver un problema.
-• Explican las relaciones métricas entre ángulos, arcos o cuerdas en la circunferencia, utilizando dibujos, esquemas o proposiciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>III Medio</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>Resolver problemas</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>OA a</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>Construir y evaluar estrategias de manera colaborativa al resolver problemas no rutinarios.</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>• Representan números complejos en el plano, relacionando con vectores e identificando las partes reales e imaginarias.
-• Utilizan los números complejos y sus representaciones pictóricas y simbólicas para encontrar solución a ecuaciones.
-• Determinan la distancia de números complejos de forma simbólica y pictórica.
-• Representan la operatoria de números complejos de forma simbólica y en el plano cartesiano.
-• Utilizan los números complejos y su operatoria para resolver problemas en modelos relacionados con los circuitos eléctricos.</t>
         </is>
       </c>
     </row>
@@ -10299,6 +10301,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>